--- a/Data/GP2_BLOOD_TRAITS.xlsx
+++ b/Data/GP2_BLOOD_TRAITS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Guinea-Pig-data_2\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CEF081-1742-447A-941C-E3EC714F306B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CFD897-55AE-4139-9445-3DDE5E3961AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1B3FF54D-4D04-4FC9-AD64-60A5BE9D2C70}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{1B3FF54D-4D04-4FC9-AD64-60A5BE9D2C70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -615,18 +615,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EB7A20-23B3-4962-A920-1FADD0CAAEA4}">
   <dimension ref="A1:Z17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="1" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -706,7 +706,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>43</v>
       </c>
@@ -786,7 +786,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>43</v>
       </c>
@@ -866,7 +866,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -946,7 +946,7 @@
         <v>3.8</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>44</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>44</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>45</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>45</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>45</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>46</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>46</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
